--- a/Reporte_Login_Alex.xlsx
+++ b/Reporte_Login_Alex.xlsx
@@ -29,7 +29,7 @@
     <t>Acceso Correcto</t>
   </si>
   <si>
-    <t>2026-06-08T00:34:30.779659500</t>
+    <t>2026-06-15T14:44:39.532216700</t>
   </si>
 </sst>
 </file>
